--- a/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Luisa Martinez\Documents\NetBeansProjects\OCXRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725C1C65-51CB-4EE2-A6E4-68C49B181AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1F17B5-4740-45FB-8EA4-F545CE1E8165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F173C3BF-BF45-4085-9BA4-BD846F4D371B}"/>
+    <workbookView xWindow="4800" yWindow="2640" windowWidth="14400" windowHeight="8170" xr2:uid="{F173C3BF-BF45-4085-9BA4-BD846F4D371B}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIOS" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>USUARIO</t>
   </si>
@@ -66,6 +66,24 @@
   </si>
   <si>
     <t>AREA</t>
+  </si>
+  <si>
+    <t>Patron</t>
+  </si>
+  <si>
+    <t>Jefazo</t>
+  </si>
+  <si>
+    <t>María Luisa</t>
+  </si>
+  <si>
+    <t>Desarrollador</t>
+  </si>
+  <si>
+    <t>Adderly</t>
+  </si>
+  <si>
+    <t>Facturista</t>
   </si>
 </sst>
 </file>
@@ -464,6 +482,12 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -472,6 +496,12 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -479,6 +509,12 @@
       </c>
       <c r="B4" t="s">
         <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1F17B5-4740-45FB-8EA4-F545CE1E8165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A504123-F0A6-4789-A862-7946B07E2D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4800" yWindow="2640" windowWidth="14400" windowHeight="8170" xr2:uid="{F173C3BF-BF45-4085-9BA4-BD846F4D371B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>USUARIO</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Facturista</t>
+  </si>
+  <si>
+    <t>prueba</t>
+  </si>
+  <si>
+    <t>** Selecciona una opción **</t>
   </si>
 </sst>
 </file>
@@ -455,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259A3497-F28F-45C5-97D9-93E4AAFCB59D}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
@@ -477,43 +483,57 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>15</v>
       </c>
     </row>

--- a/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>USUARIO</t>
   </si>
@@ -90,12 +90,43 @@
   </si>
   <si>
     <t>** Selecciona una opción **</t>
+  </si>
+  <si>
+    <t>PUESTO</t>
+  </si>
+  <si>
+    <t>CORREO</t>
+  </si>
+  <si>
+    <t>FIRMA</t>
+  </si>
+  <si>
+    <t>angelLira2104</t>
+  </si>
+  <si>
+    <t>Luis angel Gonzalez Lira</t>
+  </si>
+  <si>
+    <t>Direccion</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>angel21@gmail.com</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>Compras</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -461,10 +492,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259A3497-F28F-45C5-97D9-93E4AAFCB59D}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -480,6 +511,15 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">

--- a/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
   <si>
     <t>USUARIO</t>
   </si>
@@ -120,6 +120,27 @@
   </si>
   <si>
     <t>Compras</t>
+  </si>
+  <si>
+    <t>Luis angel</t>
+  </si>
+  <si>
+    <t>angelliragon@gmail.com</t>
+  </si>
+  <si>
+    <t>angelLopez21</t>
+  </si>
+  <si>
+    <t>angel lopez alejandro</t>
+  </si>
+  <si>
+    <t>RECURSOS HUMANOS</t>
+  </si>
+  <si>
+    <t>CORDINADOR</t>
+  </si>
+  <si>
+    <t>angel@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -492,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259A3497-F28F-45C5-97D9-93E4AAFCB59D}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875" collapsed="true"/>
@@ -577,6 +598,52 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>USUARIO</t>
   </si>
@@ -141,6 +141,24 @@
   </si>
   <si>
     <t>angel@gmail.com</t>
+  </si>
+  <si>
+    <t>nestor21</t>
+  </si>
+  <si>
+    <t>nestor salazar</t>
+  </si>
+  <si>
+    <t>CORDINACION</t>
+  </si>
+  <si>
+    <t>AUXILIAR</t>
+  </si>
+  <si>
+    <t>nest@gmail.com</t>
+  </si>
+  <si>
+    <t>246</t>
   </si>
 </sst>
 </file>
@@ -513,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259A3497-F28F-45C5-97D9-93E4AAFCB59D}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875" collapsed="true"/>
@@ -644,6 +662,29 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>USUARIO</t>
   </si>
@@ -90,12 +90,46 @@
   </si>
   <si>
     <t>María Luisa Martínez Morales</t>
+  </si>
+  <si>
+    <t>PUESTO</t>
+  </si>
+  <si>
+    <t>CORREO</t>
+  </si>
+  <si>
+    <t>FIRMA</t>
+  </si>
+  <si>
+    <t>angelLira2104</t>
+  </si>
+  <si>
+    <t>Luis agnel Lira</t>
+  </si>
+  <si>
+    <t>GERENCIA</t>
+  </si>
+  <si>
+    <t>SUB-GERENTE</t>
+  </si>
+  <si>
+    <t>angel@gmail.com</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>AUXILIAR</t>
+  </si>
+  <si>
+    <t>angelLira210</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -461,10 +495,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259A3497-F28F-45C5-97D9-93E4AAFCB59D}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -480,6 +514,15 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -535,6 +578,29 @@
       </c>
       <c r="D5" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/USUARIOS.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CF71FA-DE54-4566-8F16-1E3D368AD457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C599A818-6331-4304-B6D6-511DC2CDDE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F173C3BF-BF45-4085-9BA4-BD846F4D371B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>USUARIO</t>
   </si>
@@ -68,12 +68,6 @@
     <t>AREA</t>
   </si>
   <si>
-    <t>Patron</t>
-  </si>
-  <si>
-    <t>Jefazo</t>
-  </si>
-  <si>
     <t>Desarrollador</t>
   </si>
   <si>
@@ -101,18 +95,6 @@
     <t>FIRMA</t>
   </si>
   <si>
-    <t>angelLira2104</t>
-  </si>
-  <si>
-    <t>Luis agnel Lira</t>
-  </si>
-  <si>
-    <t>GERENCIA</t>
-  </si>
-  <si>
-    <t>SUB-GERENTE</t>
-  </si>
-  <si>
     <t>angel@gmail.com</t>
   </si>
   <si>
@@ -123,13 +105,21 @@
   </si>
   <si>
     <t>angelLira210</t>
+  </si>
+  <si>
+    <t>MC. Jesús Alfredo Flores Osorio</t>
+  </si>
+  <si>
+    <t>Director de Finanzas</t>
+  </si>
+  <si>
+    <t>Luis Angel Lira</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -498,10 +488,12 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.1796875" collapsed="true"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -515,30 +507,30 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -546,13 +538,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -560,13 +552,13 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -574,33 +566,33 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
